--- a/artfynd/A 25522-2025 artfynd.xlsx
+++ b/artfynd/A 25522-2025 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88270766</v>
+        <v>133029463</v>
       </c>
       <c r="B2" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Östvattnet, Ång</t>
+          <t>Östvattenmyran, Östvattenmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>551439.5404551844</v>
+        <v>551387</v>
       </c>
       <c r="R2" t="n">
-        <v>7038168.524900168</v>
+        <v>7038163</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-09-03</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,12 +770,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Niclas Vallin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Niclas Vallin</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -790,16 +785,11 @@
         <v>113511095</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -893,50 +883,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133029309</v>
+        <v>133029280</v>
       </c>
       <c r="B4" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Östvattenmyran, Östvattenmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>551440</v>
+        <v>551434</v>
       </c>
       <c r="R4" t="n">
-        <v>7038185</v>
+        <v>7038175</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,7 +953,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -978,12 +963,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:44</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133029494</v>
+        <v>133029182</v>
       </c>
       <c r="B5" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1050,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>551415</v>
+        <v>551433</v>
       </c>
       <c r="R5" t="n">
-        <v>7038140</v>
+        <v>7038194</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1065,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1095,7 +1075,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:48</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1127,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133029280</v>
+        <v>133029309</v>
       </c>
       <c r="B6" t="n">
-        <v>79334</v>
+        <v>57975</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1138,34 +1118,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Östvattenmyran, Östvattenmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>551434</v>
+        <v>551440</v>
       </c>
       <c r="R6" t="n">
-        <v>7038175</v>
+        <v>7038185</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1197,7 +1182,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1207,7 +1192,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133029463</v>
+        <v>133029494</v>
       </c>
       <c r="B7" t="n">
-        <v>79334</v>
+        <v>57975</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1245,34 +1235,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Östvattenmyran, Östvattenmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>551387</v>
+        <v>551415</v>
       </c>
       <c r="R7" t="n">
-        <v>7038163</v>
+        <v>7038140</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1304,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1314,7 +1309,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:48</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
